--- a/scripts/example_input/dummy_traject/16-X_003_DP012-DP015.xlsx
+++ b/scripts/example_input/dummy_traject/16-X_003_DP012-DP015.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKA\sources\github\faalkansbeheer\scripts\example_input\dummy_traject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8B4E86-3F34-499F-84AD-1C4126AC2C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C7725E-6F47-4563-84A7-A71357E8DFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario1" sheetId="4" r:id="rId1"/>
@@ -1361,7 +1361,7 @@
         <v>falen bij waterstand h &gt; 5</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="25"/>
       <c r="F26">
@@ -1417,17 +1417,16 @@
       <c r="D28">
         <v>5.01</v>
       </c>
-      <c r="E28" s="25"/>
-      <c r="F28">
-        <v>-20</v>
-      </c>
-      <c r="G28">
-        <f>IF(FCPunten5[[#This Row],[Beta_h]]="","",_xlfn.NORM.S.DIST(-1*FCPunten5[[#This Row],[Beta_h]],TRUE))</f>
+      <c r="E28" s="25">
         <v>1</v>
       </c>
-      <c r="H28" s="13" t="str">
-        <f>IF(FCPunten5[[#This Row],[Pf_h]]="", "",-_xlfn.NORM.S.INV(FCPunten5[[#This Row],[Pf_h]]))</f>
-        <v/>
+      <c r="G28" t="str">
+        <f>IF(FCPunten5[[#This Row],[Beta_h]]="","",_xlfn.NORM.S.DIST(-1*FCPunten5[[#This Row],[Beta_h]],TRUE))</f>
+        <v/>
+      </c>
+      <c r="H28" s="13" t="e">
+        <f>IF(FCPunten5[[#This Row],[Pf_h]]="", "",-_xlfn.NORM.S.INV(FCPunten5[[#This Row],[Pf_h]]))</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1442,19 +1441,18 @@
         <v>falen bij waterstand h &gt; 5</v>
       </c>
       <c r="D29">
-        <v>7</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29">
-        <v>-20</v>
-      </c>
-      <c r="G29">
-        <f>IF(FCPunten5[[#This Row],[Beta_h]]="","",_xlfn.NORM.S.DIST(-1*FCPunten5[[#This Row],[Beta_h]],TRUE))</f>
+        <v>10</v>
+      </c>
+      <c r="E29" s="25">
         <v>1</v>
       </c>
-      <c r="H29" s="13" t="str">
-        <f>IF(FCPunten5[[#This Row],[Pf_h]]="", "",-_xlfn.NORM.S.INV(FCPunten5[[#This Row],[Pf_h]]))</f>
-        <v/>
+      <c r="G29" t="str">
+        <f>IF(FCPunten5[[#This Row],[Beta_h]]="","",_xlfn.NORM.S.DIST(-1*FCPunten5[[#This Row],[Beta_h]],TRUE))</f>
+        <v/>
+      </c>
+      <c r="H29" s="13" t="e">
+        <f>IF(FCPunten5[[#This Row],[Pf_h]]="", "",-_xlfn.NORM.S.INV(FCPunten5[[#This Row],[Pf_h]]))</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2001,6 +1999,100 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-39893</_dlc_DocId>
+    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
+        </TermInfo>
+      </Terms>
+    </e39ed97c196f40ca8994d73dd80b64d0>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Value>2</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
+        </TermInfo>
+      </Terms>
+    </n3c4235fe90e4626a88beeb52e343114>
+    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-39893</Url>
+      <Description>CBPJ-627581585-39893</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document CB" ma:contentTypeID="0x010100A075C07AB76F2344B407AD577D6B92360100C7929242D85FED4E837C6D4097594A04" ma:contentTypeVersion="17" ma:contentTypeDescription="WSRL Document CB" ma:contentTypeScope="" ma:versionID="18c34f52c90103a5ca6273d5693675c9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="338e11dd-9b15-475b-8471-fcb79439c886" xmlns:ns3="edfbc03d-db26-4301-8719-99148ee26221" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b0dc2be265e99dcf2e366001e246f12" ns2:_="" ns3:_="">
     <xsd:import namespace="338e11dd-9b15-475b-8471-fcb79439c886"/>
@@ -2282,101 +2374,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-39893</_dlc_DocId>
-    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
-        </TermInfo>
-      </Terms>
-    </e39ed97c196f40ca8994d73dd80b64d0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Value>2</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
-        </TermInfo>
-      </Terms>
-    </n3c4235fe90e4626a88beeb52e343114>
-    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-39893</Url>
-      <Description>CBPJ-627581585-39893</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB6BAA4-1CD2-494A-9433-1FC41C42B0F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{263B6D11-DEF0-4FE0-9C65-6A39ECB04A89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633EBDFC-B21A-4048-98F2-0CE0F24CB488}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
+    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC89D3C9-3D59-4FE5-907B-98550F7D511D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2393,31 +2418,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633EBDFC-B21A-4048-98F2-0CE0F24CB488}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
-    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{263B6D11-DEF0-4FE0-9C65-6A39ECB04A89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB6BAA4-1CD2-494A-9433-1FC41C42B0F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/scripts/example_input/dummy_traject/16-X_003_DP012-DP015.xlsx
+++ b/scripts/example_input/dummy_traject/16-X_003_DP012-DP015.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKA\sources\github\faalkansbeheer\scripts\example_input\dummy_traject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C7725E-6F47-4563-84A7-A71357E8DFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803222D5-20D2-4A73-B236-6B0F105C4988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario1" sheetId="4" r:id="rId1"/>
@@ -185,9 +185,6 @@
     <t>16-X</t>
   </si>
   <si>
-    <t>groene dijk</t>
-  </si>
-  <si>
     <t>016-01_0145_9_BO_km0954</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>DP012.-DP015.</t>
+  </si>
+  <si>
+    <t>Testcase 2</t>
   </si>
 </sst>
 </file>
@@ -1097,14 +1097,14 @@
         <v>3</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5">
         <f>C6-B6</f>
         <v>300</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>40</v>
@@ -1119,10 +1119,10 @@
         <v>1100</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N6" s="24">
         <v>7</v>
@@ -1207,7 +1207,7 @@
         <v>29</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -1999,6 +1999,50 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-39893</_dlc_DocId>
+    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
+        </TermInfo>
+      </Terms>
+    </e39ed97c196f40ca8994d73dd80b64d0>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Value>2</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
+        </TermInfo>
+      </Terms>
+    </n3c4235fe90e4626a88beeb52e343114>
+    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
+      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-39893</Url>
+      <Description>CBPJ-627581585-39893</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -2046,50 +2090,6 @@
     <Filter/>
   </Receiver>
 </spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="338e11dd-9b15-475b-8471-fcb79439c886">CBPJ-627581585-39893</_dlc_DocId>
-    <e39ed97c196f40ca8994d73dd80b64d0 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Waterschap Rivierenland</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1732778-9e42-4ec7-9c76-7a14861f4695</TermId>
-        </TermInfo>
-      </Terms>
-    </e39ed97c196f40ca8994d73dd80b64d0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Value>2</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <n3c4235fe90e4626a88beeb52e343114 xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Concept</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1e89abd-99d3-43d9-9ea5-d87afe83fe15</TermId>
-        </TermInfo>
-      </Terms>
-    </n3c4235fe90e4626a88beeb52e343114>
-    <_dlc_DocIdUrl xmlns="338e11dd-9b15-475b-8471-fcb79439c886">
-      <Url>https://wsrlnl.sharepoint.com/sites/CBPR-ydjk6ItuUw/_layouts/15/DocIdRedir.aspx?ID=CBPJ-627581585-39893</Url>
-      <Description>CBPJ-627581585-39893</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2375,9 +2375,12 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB6BAA4-1CD2-494A-9433-1FC41C42B0F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633EBDFC-B21A-4048-98F2-0CE0F24CB488}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
+    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2391,12 +2394,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{633EBDFC-B21A-4048-98F2-0CE0F24CB488}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB6BAA4-1CD2-494A-9433-1FC41C42B0F8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="338e11dd-9b15-475b-8471-fcb79439c886"/>
-    <ds:schemaRef ds:uri="edfbc03d-db26-4301-8719-99148ee26221"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
